--- a/p3_data_preparation/data/germany/integrate_data/df_map_teams_fs_so.xlsx
+++ b/p3_data_preparation/data/germany/integrate_data/df_map_teams_fs_so.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>111235</v>
+        <v>100409</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>fc augsburg</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -497,20 +497,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1824</v>
+        <v>22</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>borussia dortmund</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,20 +528,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1831</v>
+        <v>1824</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>fc union berlin</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -559,30 +559,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fc koln</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>31</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>fc koln</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -590,24 +578,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>borussia dortmund</t>
+          <t>borussia monchengladbach</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -652,20 +640,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>1831</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>fc union berlin</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -683,20 +671,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>vfl wolfsburg</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -714,20 +702,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10029</v>
+        <v>32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tsg hoffenheim</t>
+          <t>bayer 04 leverkusen</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -745,20 +733,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110502</v>
+        <v>160</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>darmstadt 98</t>
+          <t>vfl bochum 1848</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -776,20 +764,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>fsv mainz 05</t>
+          <t>sc freiburg</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -807,24 +795,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>112172</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>borussia monchengladbach</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -838,20 +826,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>darmstadt</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>110502</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bayer 04 leverkusen</t>
+          <t>darmstadt 98</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -869,20 +857,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>100409</v>
+        <v>111235</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>fc augsburg</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -900,18 +888,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bayern munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10029</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tsg hoffenheim</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -919,20 +919,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>sc freiburg</t>
+          <t>fsv mainz 05</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -950,20 +950,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>112172</v>
+        <v>175</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>vfl wolfsburg</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -981,20 +981,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>fc koln</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>vfl bochum 1848</t>
+          <t>fc koln</t>
         </is>
       </c>
       <c r="F19" t="n">
